--- a/TestData/T2017_GiftLog_GiftRequestProcess_GiftRequests_VerifyTheTotalsOfTheGiftsAreMeasuredSeparatelyFromTheCurrentYear.xlsx
+++ b/TestData/T2017_GiftLog_GiftRequestProcess_GiftRequests_VerifyTheTotalsOfTheGiftsAreMeasuredSeparatelyFromTheCurrentYear.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HL\SalesForce_Project\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1669E8-CB25-43CD-A8A3-D82C88CB170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF96D15-A646-4F84-BBB6-E3B298FD3ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GiftLog" sheetId="4" r:id="rId1"/>
-    <sheet name="GiftEdit" sheetId="6" r:id="rId2"/>
-    <sheet name="Users" sheetId="5" r:id="rId3"/>
+    <sheet name="Users" sheetId="5" r:id="rId1"/>
+    <sheet name="AppName" sheetId="7" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="8" r:id="rId3"/>
+    <sheet name="GiftLog" sheetId="4" r:id="rId4"/>
+    <sheet name="GiftEdit" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>Client Gift Pre-approval</t>
   </si>
@@ -68,9 +70,6 @@
     <t>ContactName</t>
   </si>
   <si>
-    <t>Test External</t>
-  </si>
-  <si>
     <t>CongratulationsMsg</t>
   </si>
   <si>
@@ -119,31 +118,43 @@
     <t>Success:\r\nYour Gift has been updated.</t>
   </si>
   <si>
-    <t>Giorgia Cardia</t>
-  </si>
-  <si>
     <t>StandardTestCompany</t>
   </si>
   <si>
     <t>ComplianceUser</t>
   </si>
   <si>
-    <t>Julie Carthane</t>
-  </si>
-  <si>
     <t>Australian Dollar</t>
   </si>
   <si>
     <t>90.0</t>
   </si>
   <si>
-    <t>External</t>
-  </si>
-  <si>
     <t>ReceipientLastName</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>Olivia Ricketts</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Gift Requests</t>
+  </si>
+  <si>
+    <t>Zain Sheikh</t>
+  </si>
+  <si>
+    <t>Giftlog Contact</t>
+  </si>
+  <si>
+    <t>Contact</t>
   </si>
 </sst>
 </file>
@@ -187,11 +198,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -473,6 +487,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67388AF-9F74-4C54-B94B-6A039B67E708}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15AF2AD5-13B7-4568-8D2D-B52D473677BD}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -496,7 +581,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -505,7 +590,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -523,30 +608,30 @@
         <v>1</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
+      <c r="B2" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -555,22 +640,22 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -579,7 +664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -601,7 +686,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -613,67 +698,36 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
